--- a/output/roomself_excel/9275.xlsx
+++ b/output/roomself_excel/9275.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25344</v>
+        <v>69582</v>
       </c>
       <c r="D2" t="n">
-        <v>1280</v>
+        <v>2400</v>
       </c>
       <c r="E2" t="n">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="F2" t="n">
-        <v>178</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>328111</v>
+        <v>187720</v>
       </c>
       <c r="D3" t="n">
-        <v>6228</v>
+        <v>3872</v>
       </c>
       <c r="E3" t="n">
-        <v>868</v>
+        <v>520</v>
       </c>
       <c r="F3" t="n">
-        <v>190</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50336</v>
+        <v>118220</v>
       </c>
       <c r="D4" t="n">
-        <v>1848</v>
+        <v>2868</v>
       </c>
       <c r="E4" t="n">
-        <v>286</v>
+        <v>434</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20280</v>
+        <v>82368</v>
       </c>
       <c r="D5" t="n">
-        <v>1144</v>
+        <v>2304</v>
       </c>
       <c r="E5" t="n">
-        <v>209</v>
+        <v>312</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>118220</v>
+        <v>50336</v>
       </c>
       <c r="D6" t="n">
-        <v>2868</v>
+        <v>1848</v>
       </c>
       <c r="E6" t="n">
-        <v>635</v>
+        <v>286</v>
       </c>
       <c r="F6" t="n">
-        <v>242</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18954</v>
+        <v>70809</v>
       </c>
       <c r="D8" t="n">
-        <v>1116</v>
+        <v>2244</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -620,17 +620,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>82368</v>
+        <v>24704</v>
       </c>
       <c r="D9" t="n">
-        <v>2304</v>
+        <v>1284</v>
       </c>
       <c r="E9" t="n">
-        <v>312</v>
+        <v>138</v>
       </c>
       <c r="F9" t="n">
         <v>35</v>
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24704</v>
+        <v>18954</v>
       </c>
       <c r="D10" t="n">
-        <v>1284</v>
+        <v>1116</v>
       </c>
       <c r="E10" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -678,6 +678,50 @@
       </c>
       <c r="F11" t="n">
         <v>181</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25344</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E12" t="n">
+        <v>197</v>
+      </c>
+      <c r="F12" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20280</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1144</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/9275.xlsx
+++ b/output/roomself_excel/9275.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>2400</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>139</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>34</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,31 @@
       <c r="D3" t="n">
         <v>3872</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>520</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>34</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>448</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +584,31 @@
       <c r="D4" t="n">
         <v>2868</v>
       </c>
-      <c r="E4" t="n">
-        <v>434</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>225</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>204</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,31 @@
       <c r="D5" t="n">
         <v>2304</v>
       </c>
-      <c r="E5" t="n">
-        <v>312</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
+        <v>264</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>304</v>
+      </c>
+      <c r="J5" t="n">
         <v>35</v>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,23 @@
       <c r="D6" t="n">
         <v>1848</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>286</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>21</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,15 @@
       <c r="D7" t="n">
         <v>1020</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,15 @@
       <c r="D8" t="n">
         <v>2244</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +749,23 @@
       <c r="D9" t="n">
         <v>1284</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>138</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>35</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +782,23 @@
       <c r="D10" t="n">
         <v>1116</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +815,38 @@
       <c r="D11" t="n">
         <v>1324</v>
       </c>
-      <c r="E11" t="n">
-        <v>201</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>181</v>
+        <v>185</v>
+      </c>
+      <c r="G11" t="n">
+        <v>17</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>185</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>146</v>
+      </c>
+      <c r="M11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +864,31 @@
       <c r="D12" t="n">
         <v>1280</v>
       </c>
-      <c r="E12" t="n">
-        <v>197</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>178</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="G12" t="n">
+        <v>34</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>144</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +905,15 @@
       <c r="D13" t="n">
         <v>1144</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/9275.xlsx
+++ b/output/roomself_excel/9275.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,46 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -527,6 +567,26 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>34</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -568,6 +628,38 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>328</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>34</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>82</v>
+      </c>
+      <c r="U3" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -609,6 +701,26 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>35</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -650,6 +762,26 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>35</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -683,6 +815,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -708,6 +848,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -733,6 +881,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -766,6 +922,26 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>35</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -799,6 +975,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -848,6 +1032,38 @@
       <c r="M11" t="n">
         <v>16</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>18</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>88</v>
+      </c>
+      <c r="U11" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -889,6 +1105,26 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>34</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -914,6 +1150,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
